--- a/rag_test_questions.xlsx
+++ b/rag_test_questions.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/ismail_shaikh_orange_com/Documents/Documents/Developer/github-personal/CrowAi/Project1/learning_crew/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/ismail_shaikh_orange_com/Documents/Documents/Developer/github-personal/CrowAi/Project1/New folder/doc_rag_demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_F1DF2C39349FD38EEDD4CFBAD39EF2756954A989" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C83FA56C-5646-492D-BC14-D9304F61DFF6}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_F1DF2C39349FD38EEDD4CFBAD39EF2756954A989" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D00C6FD-370E-4EE3-83D6-CAB3BDF72E1D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Questions" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="45">
   <si>
     <t>No.</t>
   </si>
@@ -149,6 +149,28 @@
   </si>
   <si>
     <t>Partial → leaning N</t>
+  </si>
+  <si>
+    <t>According to Table 5.1 - Leave entitlements for FT-R employees, India entity. Pro-rated for FTC, PT and mid-year joiners, employees are entitled to 12 sick leave days.</t>
+  </si>
+  <si>
+    <t>Unfortunately, the retrieved passages do not contain enough information to provide a clear and accurate answer to the question "What's the vacation policy?".
+The passages provide some details on leave entitlements and the process for applying for leave, but they do not explicitly state how the vacation policy works. The leave year is defined as running from 01 January to 31 December, and all leave is applied for in Workbench, but the specifics of the vacation policy, such as the accrual rate, carry-forward limits, and encashable balance, are not discussed.
+Additionally, the passages mention that the leave entitlements are pro-rated for different types of employees (FT-R, FTC, PT, and mid-year joiners), but they do not provide details on how the vacation policy varies for different employee groups.
+Therefore, I must conclude that the retrieved passages do not contain sufficient information to provide an accurate answer to the question.</t>
+  </si>
+  <si>
+    <t>How many days of sick leave are carried forward if an employee doesn't use them in a year?</t>
+  </si>
+  <si>
+    <t>Based on the retrieved passage from the "employee_handbook.pdf" document, the answer to the original question is:
+**No sick leave days are carried forward if an employee doesn't use them in a year.**
+ Passage content:
+**Sick Leave:**
+| Leave type          | Entitlement           | Accrual       | Carry-forward   | Encashable   |
+|---------------------|-----------------------|---------------|-----------------|--------------|
+| Sick                | 12 days               | Front-loaded  | No              | No           |
+This passage indicates that the "Carry-forward" option for Sick Leave is marked as "No", which means that any unused sick leave days are not carried forward to the next year.</t>
   </si>
 </sst>
 </file>
@@ -190,7 +212,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -213,17 +235,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -310,10 +349,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -708,6 +743,152 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89DC6C2-CBE4-4188-93FA-A766E72DB18F}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="78.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="225" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="240" x14ac:dyDescent="0.25">
+      <c r="C8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e6c818a6-e1a0-4a6e-a969-20d857c5dc62}" enabled="1" method="Standard" siteId="{90c7a20a-f34b-40bf-bc48-b9253b6f5d20}" removed="0"/>

--- a/rag_test_questions.xlsx
+++ b/rag_test_questions.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="68" documentId="11_F1DF2C39349FD38EEDD4CFBAD39EF2756954A989" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D00C6FD-370E-4EE3-83D6-CAB3BDF72E1D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="29145" yWindow="345" windowWidth="19320" windowHeight="10020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Questions" sheetId="1" r:id="rId1"/>

--- a/rag_test_questions.xlsx
+++ b/rag_test_questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/ismail_shaikh_orange_com/Documents/Documents/Developer/github-personal/CrowAi/Project1/New folder/doc_rag_demo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/ismail_shaikh_orange_com/Documents/Documents/Developer/github-personal/CrowAi/Project1/New folder1/doc_rag_demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="68" documentId="11_F1DF2C39349FD38EEDD4CFBAD39EF2756954A989" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D00C6FD-370E-4EE3-83D6-CAB3BDF72E1D}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="29145" yWindow="345" windowWidth="19320" windowHeight="10020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Questions" sheetId="1" r:id="rId1"/>
